--- a/data/trans_orig/P23_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P23_R-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2007</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>343415</t>
+          <t>343258</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>403370</t>
+          <t>403903</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>152741</t>
+          <t>151270</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>202332</t>
+          <t>201274</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>512316</t>
+          <t>511026</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>598216</t>
+          <t>592873</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>627311</t>
+          <t>626778</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>687266</t>
+          <t>687423</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1112781</t>
+          <t>1113839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1162372</t>
+          <t>1163843</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1747577</t>
+          <t>1752920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1833477</t>
+          <t>1834767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>776435</t>
+          <t>776392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>856802</t>
+          <t>860662</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>512636</t>
+          <t>511913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>587509</t>
+          <t>586028</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1310990</t>
+          <t>1314119</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1421728</t>
+          <t>1422658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,36%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>836611</t>
+          <t>832751</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>916978</t>
+          <t>917021</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1000164</t>
+          <t>1001645</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1075037</t>
+          <t>1075760</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1859358</t>
+          <t>1858428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1970096</t>
+          <t>1966967</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,95%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>171606</t>
+          <t>172156</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>215756</t>
+          <t>218160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118092</t>
+          <t>118718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160162</t>
+          <t>157472</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>305186</t>
+          <t>298590</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>364147</t>
+          <t>360368</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>335652</t>
+          <t>333248</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>379802</t>
+          <t>379252</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>316250</t>
+          <t>318940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>358320</t>
+          <t>357694</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>663673</t>
+          <t>667452</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>722634</t>
+          <t>729230</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1325414</t>
+          <t>1329366</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1442511</t>
+          <t>1446641</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>814610</t>
+          <t>815961</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>918767</t>
+          <t>910974</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2170312</t>
+          <t>2166858</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2328069</t>
+          <t>2330261</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,02%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1832990</t>
+          <t>1828860</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1950087</t>
+          <t>1946135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2460430</t>
+          <t>2468223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2564587</t>
+          <t>2563236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4326629</t>
+          <t>4324437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4484386</t>
+          <t>4487840</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,44%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2012</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>304493</t>
+          <t>305920</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>367080</t>
+          <t>364630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>174531</t>
+          <t>174524</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>227111</t>
+          <t>226179</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>494288</t>
+          <t>496028</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>576840</t>
+          <t>575016</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>607563</t>
+          <t>610013</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>670150</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1110686</t>
+          <t>1111618</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1163266</t>
+          <t>1163273</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1735600</t>
+          <t>1737424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1818152</t>
+          <t>1816412</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>809829</t>
+          <t>809383</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>901014</t>
+          <t>899273</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>596326</t>
+          <t>594334</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>674362</t>
+          <t>681069</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1426527</t>
+          <t>1431162</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1552200</t>
+          <t>1554068</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1061914</t>
+          <t>1063655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1153099</t>
+          <t>1153545</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1081459</t>
+          <t>1074752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1159495</t>
+          <t>1161487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2166548</t>
+          <t>2164680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2292221</t>
+          <t>2287586</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,51%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141496</t>
+          <t>142337</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>185384</t>
+          <t>186266</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>120165</t>
+          <t>119601</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161618</t>
+          <t>160980</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269212</t>
+          <t>268541</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>330702</t>
+          <t>330776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295797</t>
+          <t>294915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>339685</t>
+          <t>338844</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>297013</t>
+          <t>297651</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338466</t>
+          <t>339030</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,76%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>609111</t>
+          <t>609037</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>670601</t>
+          <t>671272</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>71,43%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1287856</t>
+          <t>1292537</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1408934</t>
+          <t>1410444</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>920751</t>
+          <t>922325</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1029355</t>
+          <t>1029308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2248048</t>
+          <t>2245923</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2420260</t>
+          <t>2410285</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,58%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2009818</t>
+          <t>2008308</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2130896</t>
+          <t>2126215</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2522893</t>
+          <t>2522940</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2631497</t>
+          <t>2629923</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4550740</t>
+          <t>4560715</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4722952</t>
+          <t>4725077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>67,78%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2016</t>
+          <t>Población que fuma diariamente tabaco y/o marihuana/hachís en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>201325</t>
+          <t>199850</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>251110</t>
+          <t>248706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116721</t>
+          <t>114211</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>158762</t>
+          <t>159950</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>327859</t>
+          <t>324724</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>393831</t>
+          <t>395155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>502372</t>
+          <t>504776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>552157</t>
+          <t>553632</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>833504</t>
+          <t>832316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>875545</t>
+          <t>878055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1351917</t>
+          <t>1350593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1417889</t>
+          <t>1421024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,4%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>771960</t>
+          <t>768647</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>861452</t>
+          <t>862257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>621697</t>
+          <t>620156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>700932</t>
+          <t>701912</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1419959</t>
+          <t>1416366</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1536556</t>
+          <t>1542879</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,98%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1214933</t>
+          <t>1214128</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1304425</t>
+          <t>1307738</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1285252</t>
+          <t>1284272</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1364487</t>
+          <t>1366028</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2526012</t>
+          <t>2519689</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2642609</t>
+          <t>2646202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>119147</t>
+          <t>118753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162089</t>
+          <t>162069</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>100729</t>
+          <t>103734</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140995</t>
+          <t>141885</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>233695</t>
+          <t>233292</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>293782</t>
+          <t>292393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>383725</t>
+          <t>383745</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>426667</t>
+          <t>427061</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>407218</t>
+          <t>406328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>447484</t>
+          <t>444479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>800245</t>
+          <t>801634</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>860332</t>
+          <t>860735</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,68%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1123252</t>
+          <t>1124670</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1230497</t>
+          <t>1236113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>868743</t>
+          <t>865306</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>974982</t>
+          <t>972186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2027632</t>
+          <t>2015941</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2174506</t>
+          <t>2175298</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,52%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2145184</t>
+          <t>2139568</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2252429</t>
+          <t>2251011</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2551680</t>
+          <t>2554476</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2657919</t>
+          <t>2661356</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4727837</t>
+          <t>4727045</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4874711</t>
+          <t>4886402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P23_R-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>343258</t>
+          <t>343070</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>403903</t>
+          <t>407942</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>151270</t>
+          <t>152886</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>201274</t>
+          <t>203466</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>511026</t>
+          <t>510377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>592873</t>
+          <t>592930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,28%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>626778</t>
+          <t>622739</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>687423</t>
+          <t>687611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1113839</t>
+          <t>1111647</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1163843</t>
+          <t>1162227</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1752920</t>
+          <t>1752863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1834767</t>
+          <t>1835416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,24%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>776392</t>
+          <t>777751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>860662</t>
+          <t>853855</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>511913</t>
+          <t>513991</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>586028</t>
+          <t>584449</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1314119</t>
+          <t>1304468</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1422658</t>
+          <t>1419599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,27%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>832751</t>
+          <t>839558</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>917021</t>
+          <t>915662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1001645</t>
+          <t>1003224</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1075760</t>
+          <t>1073682</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1858428</t>
+          <t>1861487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1966967</t>
+          <t>1976618</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>172156</t>
+          <t>171191</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>218160</t>
+          <t>215947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,56%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>118718</t>
+          <t>120836</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157472</t>
+          <t>160485</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>298590</t>
+          <t>302193</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>360368</t>
+          <t>357854</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>333248</t>
+          <t>335461</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>379252</t>
+          <t>380217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318940</t>
+          <t>315927</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>357694</t>
+          <t>355576</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>667452</t>
+          <t>669966</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>729230</t>
+          <t>725627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,6%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1329366</t>
+          <t>1331274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1446641</t>
+          <t>1442553</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>815961</t>
+          <t>815438</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>910974</t>
+          <t>919173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2166858</t>
+          <t>2173732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2330261</t>
+          <t>2325182</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1828860</t>
+          <t>1832948</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1946135</t>
+          <t>1944227</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2468223</t>
+          <t>2460024</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2563236</t>
+          <t>2563759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4324437</t>
+          <t>4329516</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4487840</t>
+          <t>4480966</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>65,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,34%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>305920</t>
+          <t>303467</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>364630</t>
+          <t>364886</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>174524</t>
+          <t>174847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>226179</t>
+          <t>227068</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>496028</t>
+          <t>492818</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>575016</t>
+          <t>574832</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>610013</t>
+          <t>609757</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>671176</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,59%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,61%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1111618</t>
+          <t>1110729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1163273</t>
+          <t>1162950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1737424</t>
+          <t>1737608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1816412</t>
+          <t>1819622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,69%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>809383</t>
+          <t>812238</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>899273</t>
+          <t>899519</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>594334</t>
+          <t>598914</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>681069</t>
+          <t>676508</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1431162</t>
+          <t>1428581</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1554068</t>
+          <t>1555373</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1063655</t>
+          <t>1063409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1153545</t>
+          <t>1150690</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1074752</t>
+          <t>1079313</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1161487</t>
+          <t>1156907</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2164680</t>
+          <t>2163375</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2287586</t>
+          <t>2290167</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142337</t>
+          <t>142206</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>186266</t>
+          <t>183992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>119601</t>
+          <t>118996</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160980</t>
+          <t>161780</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>268541</t>
+          <t>271135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>330776</t>
+          <t>330740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,19%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>294915</t>
+          <t>297189</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>338844</t>
+          <t>338975</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>297651</t>
+          <t>296851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>339030</t>
+          <t>339635</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>609037</t>
+          <t>609073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>671272</t>
+          <t>668678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>71,15%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1292537</t>
+          <t>1291250</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1410444</t>
+          <t>1409139</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>922325</t>
+          <t>921679</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1029308</t>
+          <t>1032651</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2245923</t>
+          <t>2245598</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2410285</t>
+          <t>2410048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,57%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2008308</t>
+          <t>2009613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2126215</t>
+          <t>2127502</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2522940</t>
+          <t>2519597</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2629923</t>
+          <t>2630569</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4560715</t>
+          <t>4560952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4725077</t>
+          <t>4725402</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,79%</t>
         </is>
       </c>
     </row>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>199850</t>
+          <t>202974</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>248706</t>
+          <t>254062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114211</t>
+          <t>116831</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>159950</t>
+          <t>160636</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>324724</t>
+          <t>330072</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>395155</t>
+          <t>397174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,12 +4023,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>504776</t>
+          <t>499420</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>553632</t>
+          <t>550508</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>832316</t>
+          <t>831630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>878055</t>
+          <t>875435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1350593</t>
+          <t>1348574</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1421024</t>
+          <t>1415676</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,09%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>768647</t>
+          <t>768343</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>862257</t>
+          <t>859360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>620156</t>
+          <t>620750</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>701912</t>
+          <t>703139</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,12 +4331,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1416366</t>
+          <t>1417667</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1542879</t>
+          <t>1536575</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1214128</t>
+          <t>1217025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1307738</t>
+          <t>1308042</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1284272</t>
+          <t>1283045</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1366028</t>
+          <t>1365434</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2519689</t>
+          <t>2525993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2646202</t>
+          <t>2644901</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,1%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118753</t>
+          <t>118932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162069</t>
+          <t>161596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103734</t>
+          <t>104369</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141885</t>
+          <t>143522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>233292</t>
+          <t>233363</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>292393</t>
+          <t>289182</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4709,12 +4709,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>383745</t>
+          <t>384218</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>427061</t>
+          <t>426882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>406328</t>
+          <t>404691</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>444479</t>
+          <t>443844</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>801634</t>
+          <t>804845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>860735</t>
+          <t>860664</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,12 +4822,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,67%</t>
         </is>
       </c>
     </row>
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1124670</t>
+          <t>1118997</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1236113</t>
+          <t>1234423</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>865306</t>
+          <t>861684</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>972186</t>
+          <t>975279</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2015941</t>
+          <t>2028494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2175298</t>
+          <t>2175877</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2139568</t>
+          <t>2141258</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2251011</t>
+          <t>2256684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2554476</t>
+          <t>2551383</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2661356</t>
+          <t>2664978</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4727045</t>
+          <t>4726466</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4886402</t>
+          <t>4873849</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,61%</t>
         </is>
       </c>
     </row>
